--- a/jira_export_2026-07-22.xlsx
+++ b/jira_export_2026-07-22.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>34,933 €</t>
+          <t>36,445 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8,677 €</t>
+          <t>10,189 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>431 h</t>
+          <t>437 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>2016</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>183.27</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18">
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         <v>1890</v>
       </c>
       <c r="O35" s="17" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="P35" s="13" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36">
@@ -3382,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>1189.5</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>951.6</v>
+        <v>432.55</v>
       </c>
     </row>
     <row r="38">
@@ -12450,7 +12450,7 @@
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
@@ -13196,10 +13196,10 @@
         <v>69305.66</v>
       </c>
       <c r="O179" s="19" t="n">
-        <v>34933.07</v>
+        <v>36445.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>130.1</v>
+        <v>132.65</v>
       </c>
     </row>
   </sheetData>
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>144.75</v>
+        <v>149.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.5</v>
@@ -14199,7 +14199,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>180.25</v>
+        <v>185</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>49.75</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>79.75</v>
+        <v>81.25</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -14229,7 +14229,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>86.5</v>
+        <v>88</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>16.75</v>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -14336,10 +14336,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>390200</v>
+        <v>388688</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>202993</v>
+        <v>201481</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>187207</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>183733</v>
+        <v>182221</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>77024</v>
+        <v>75512</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106709</v>
@@ -14415,7 +14415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14439,7 +14439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 12 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14494,22 +14494,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -14539,22 +14539,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34621</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00176431</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
@@ -14584,22 +14584,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -14619,32 +14619,32 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34566</t>
+          <t>PDMDEP-34621</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34559</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00154892</t>
+          <t>00176431</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
@@ -14674,22 +14674,22 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -14709,32 +14709,32 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -14754,32 +14754,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -14799,32 +14799,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -14834,7 +14834,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -14844,32 +14844,32 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>4475</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -14889,32 +14889,32 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>2035</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -14934,42 +14934,42 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>250</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -14979,104 +14979,152 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>0</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-34396</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34390</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Commune Le THOR</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>00171793</t>
+        </is>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34654</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34650</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>00176582</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I16" s="27" t="n">
-        <v>4300</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>12 commande(s)</t>
-        </is>
-      </c>
-      <c r="I17" s="25" t="n">
-        <v>14910</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="27" t="n">
         <v>4300</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" s="18" t="n"/>
@@ -15087,11 +15135,53 @@
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>10 commande(s)</t>
+          <t>14 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="25" t="n">
-        <v>10610</v>
+        <v>19910</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>12 commande(s)</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="n">
+        <v>15610</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-22.xlsx
+++ b/jira_export_2026-07-22.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>437 h</t>
+          <t>440 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>2016</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>168</v>
+        <v>161.28</v>
       </c>
     </row>
     <row r="18">
@@ -12450,7 +12450,7 @@
         <v>34</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>34</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="L171" s="12" t="inlineStr"/>
       <c r="M171" s="12" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
         <v>36445.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>132.65</v>
+        <v>132.17</v>
       </c>
     </row>
   </sheetData>
@@ -14190,16 +14190,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>149.5</v>
+        <v>150.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>32.5</v>
+        <v>32.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>49.75</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>92.33</v>
+        <v>94.08</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-22.xlsx
+++ b/jira_export_2026-07-22.xlsx
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -11002,7 +11002,7 @@
         <v>15</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>36445.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>132.17</v>
+        <v>131.93</v>
       </c>
     </row>
   </sheetData>
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>150.25</v>
+        <v>150.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.75</v>
@@ -14199,7 +14199,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>186</v>
+        <v>186.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>49.75</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14439,7 +14439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 14 commande(s)</t>
+          <t>Épics créées ce mois — 15 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14494,12 +14494,12 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -14539,12 +14539,12 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -14584,22 +14584,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
@@ -14629,22 +14629,22 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34621</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00176431</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
@@ -14674,22 +14674,22 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34621</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -14709,44 +14709,44 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176431</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>1300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34566</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34559</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
+          <t>COMMUNE DE RIEZ</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Services</t>
@@ -14754,32 +14754,32 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00154892</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>5000</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34545</t>
+          <t>PDMDEP-34566</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34559</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -14799,32 +14799,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00173172</t>
+          <t>00154892</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34545</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -14844,32 +14844,32 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00173172</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -14889,22 +14889,22 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>1050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -14934,32 +14934,32 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>4475</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -14979,32 +14979,32 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>2035</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34396</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34390</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Commune Le THOR</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -15024,37 +15024,37 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00171793</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>250</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34396</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34390</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune Le THOR</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -15069,83 +15069,107 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00171793</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-34654</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34650</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>00176582</t>
+        </is>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I18" s="27" t="n">
+      <c r="I19" s="26" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>14 commande(s)</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>19910</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B20" s="18" t="n"/>
@@ -15156,17 +15180,17 @@
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>2 commande(s)</t>
+          <t>15 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="25" t="n">
-        <v>4300</v>
+        <v>19910</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B21" s="18" t="n"/>
@@ -15177,10 +15201,31 @@
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>12 commande(s)</t>
+          <t>2 commande(s)</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>13 commande(s)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="n">
         <v>15610</v>
       </c>
     </row>
